--- a/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
+++ b/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:22:45+00:00</t>
+    <t>2026-06-10T12:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
+++ b/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:24:33+00:00</t>
+    <t>2026-06-10T12:26:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
+++ b/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:26:33+00:00</t>
+    <t>2026-06-10T12:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
+++ b/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:45:37+00:00</t>
+    <t>2026-06-10T12:57:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
+++ b/main/ig/StructureDefinition-ror-limite-caracteristique-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:57:58+00:00</t>
+    <t>2026-07-07T12:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
